--- a/Lists/K-Controller Command overview.xlsx
+++ b/Lists/K-Controller Command overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://masterx-my.sharepoint.com/personal/arve_daae_solberg_kd_kongsberg_com/Documents/Summer project 2025/Ros2_kctrl_wrapper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{9ABA8214-ECD9-4205-98CD-1F312BE5AE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C16191F-2B23-4955-B2F5-FD8C3EF0B2A5}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="8_{9ABA8214-ECD9-4205-98CD-1F312BE5AE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F39301DF-2FAD-41AB-B63F-6C2FF3597904}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{51D9D6FA-36B6-45AD-A727-826874252223}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{51D9D6FA-36B6-45AD-A727-826874252223}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -741,7 +741,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -774,12 +774,19 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -789,21 +796,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -820,10 +812,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1177,8 +1165,7 @@
       <c r="G1" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="20"/>
-      <c r="J1" s="21"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -1195,11 +1182,10 @@
       <c r="F2" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="G2" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="20"/>
-      <c r="J2" s="22"/>
+      <c r="G2" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="14"/>
       <c r="X2" t="s">
         <v>116</v>
       </c>
@@ -1223,11 +1209,10 @@
       <c r="F3" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="G3" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="22"/>
+      <c r="G3" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -1248,11 +1233,10 @@
       <c r="F4" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="G4" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="20"/>
-      <c r="J4" s="22"/>
+      <c r="G4" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="14"/>
     </row>
     <row r="5" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -1271,11 +1255,10 @@
       <c r="F5" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="20"/>
-      <c r="J5" s="22"/>
+      <c r="G5" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -1299,8 +1282,6 @@
       <c r="G6" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
     </row>
     <row r="7" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -1324,8 +1305,6 @@
       <c r="G7" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
     </row>
     <row r="8" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -1346,11 +1325,10 @@
       <c r="F8" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G8" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="23"/>
+      <c r="G8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="16"/>
     </row>
     <row r="9" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -1371,11 +1349,10 @@
       <c r="F9" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G9" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="20"/>
-      <c r="J9" s="23"/>
+      <c r="G9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="16"/>
     </row>
     <row r="10" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
@@ -1396,11 +1373,10 @@
       <c r="F10" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G10" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" s="20"/>
-      <c r="J10" s="22"/>
+      <c r="G10" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="14"/>
     </row>
     <row r="11" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -1421,11 +1397,10 @@
       <c r="F11" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G11" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="20"/>
-      <c r="J11" s="22"/>
+      <c r="G11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
@@ -1446,11 +1421,10 @@
       <c r="F12" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G12" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="20"/>
-      <c r="J12" s="22"/>
+      <c r="G12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="14"/>
     </row>
     <row r="13" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
@@ -1469,11 +1443,10 @@
       <c r="F13" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="20"/>
-      <c r="J13" s="22"/>
+      <c r="G13" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
@@ -1494,11 +1467,10 @@
       <c r="F14" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="20"/>
-      <c r="J14" s="22"/>
+      <c r="G14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="14"/>
     </row>
     <row r="15" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
@@ -1519,11 +1491,10 @@
       <c r="F15" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" s="20"/>
-      <c r="J15" s="22"/>
+      <c r="G15" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="14"/>
     </row>
     <row r="16" spans="1:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -1542,11 +1513,10 @@
       <c r="F16" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="G16" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="20"/>
-      <c r="J16" s="22"/>
+      <c r="G16" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="14"/>
     </row>
     <row r="17" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -1565,11 +1535,10 @@
       <c r="F17" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="G17" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="20"/>
-      <c r="J17" s="22"/>
+      <c r="G17" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="14"/>
     </row>
     <row r="18" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
@@ -1588,11 +1557,10 @@
       <c r="F18" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="G18" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" s="20"/>
-      <c r="J18" s="22"/>
+      <c r="G18" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="14"/>
     </row>
     <row r="19" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
@@ -1611,11 +1579,10 @@
       <c r="F19" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="G19" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="20"/>
-      <c r="J19" s="22"/>
+      <c r="G19" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="14"/>
     </row>
     <row r="20" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -1634,11 +1601,10 @@
       <c r="F20" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G20" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" s="20"/>
-      <c r="J20" s="22"/>
+      <c r="G20" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" s="14"/>
     </row>
     <row r="21" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
@@ -1657,11 +1623,10 @@
       <c r="F21" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G21" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" s="20"/>
-      <c r="J21" s="22"/>
+      <c r="G21" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="14"/>
     </row>
     <row r="22" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
@@ -1682,11 +1647,10 @@
       <c r="F22" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" s="20"/>
-      <c r="J22" s="22"/>
+      <c r="G22" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" s="14"/>
     </row>
     <row r="23" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
@@ -1705,47 +1669,46 @@
       <c r="F23" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G23" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" s="20"/>
-      <c r="J23" s="22"/>
+      <c r="G23" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="14"/>
     </row>
     <row r="24" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="16"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F24" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" s="24"/>
-      <c r="J24" s="25"/>
+      <c r="F24" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="17"/>
+      <c r="J24" s="18"/>
     </row>
     <row r="25" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="18"/>
-      <c r="G25" s="15"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="25"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="18"/>
     </row>
     <row r="26" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
@@ -1767,8 +1730,7 @@
       <c r="G26" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I26" s="20"/>
-      <c r="J26" s="22"/>
+      <c r="J26" s="14"/>
     </row>
     <row r="27" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
@@ -1787,12 +1749,11 @@
       <c r="F27" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" s="20"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="19"/>
+      <c r="G27" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
     </row>
     <row r="28" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
@@ -1813,11 +1774,10 @@
       <c r="F28" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G28" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" s="20"/>
-      <c r="J28" s="22"/>
+      <c r="G28" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" s="14"/>
     </row>
     <row r="29" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
@@ -1839,8 +1799,7 @@
       <c r="G29" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I29" s="20"/>
-      <c r="J29" s="22"/>
+      <c r="J29" s="14"/>
     </row>
     <row r="30" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
@@ -1864,8 +1823,7 @@
       <c r="G30" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I30" s="20"/>
-      <c r="J30" s="22"/>
+      <c r="J30" s="14"/>
     </row>
     <row r="31" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
@@ -1889,8 +1847,6 @@
       <c r="G31" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
     </row>
     <row r="32" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
@@ -1914,10 +1870,8 @@
       <c r="G32" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-    </row>
-    <row r="33" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>103</v>
       </c>
@@ -1936,13 +1890,11 @@
       <c r="F33" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-    </row>
-    <row r="34" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G33" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>112</v>
       </c>
@@ -1961,65 +1913,63 @@
       <c r="F34" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="G34" s="26" t="b">
+      <c r="G34" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G35" s="27"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G36" s="27"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G37" s="27"/>
-    </row>
-    <row r="38" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G35" s="20"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G36" s="20"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G37" s="20"/>
+    </row>
+    <row r="38" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
-      <c r="G38" s="27"/>
-    </row>
-    <row r="39" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="20"/>
+    </row>
+    <row r="39" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
-      <c r="G39" s="27"/>
-    </row>
-    <row r="40" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="20"/>
+    </row>
+    <row r="40" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
-      <c r="G40" s="27"/>
-    </row>
-    <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="20"/>
+    </row>
+    <row r="41" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
     </row>
-    <row r="42" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
     </row>
-    <row r="43" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
     </row>
-    <row r="44" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
     </row>
-    <row r="45" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
     </row>
-    <row r="46" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
     </row>
-    <row r="47" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
     </row>
-    <row r="48" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
     </row>
